--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,36 @@
       </c>
       <c r="C7" t="n">
         <v>15000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Usuario F</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Usuario SD</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4000</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,21 @@
       </c>
       <c r="C9" t="n">
         <v>4000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Usuario SDS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15000</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,7 +579,52 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NLLK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Usuario NLLK</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>15000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Usuario QW</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SFW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Usuario SFW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1115</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,66 @@
       </c>
       <c r="C13" t="n">
         <v>1115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SDA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Usuario SDA</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Usuario QER</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QWDQ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Usuario QWDQ</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DQWD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Usuario DQWD</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,21 @@
       </c>
       <c r="C17" t="n">
         <v>20000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FREW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Usuario FREW</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Products" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Config" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,81 @@
       </c>
       <c r="C18" t="n">
         <v>3000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SDF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Usuario SDF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Usuario ASD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ASAF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Usuario ASAF</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HHUI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Usuario HHUI</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SVSD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Usuario SVSD</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="4">
@@ -489,291 +489,6 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WER</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Usuario WER</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KJJH</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Usuario KJJH</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Usuario WE</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Usuario F</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Usuario SD</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Usuario SDS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NLLK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Usuario NLLK</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>QW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Usuario QW</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SFW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Usuario SFW</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SDA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Usuario SDA</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>QER</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Usuario QER</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>QWDQ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Usuario QWDQ</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DQWD</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Usuario DQWD</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FREW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Usuario FREW</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SDF</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Usuario SDF</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ASD</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Usuario ASD</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ASAF</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Usuario ASAF</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HHUI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Usuario HHUI</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SVSD</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Usuario SVSD</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1014,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,6 +754,46 @@
         <v>50</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mixed_attempts</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mixed_success</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>recovery_attempts</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recovery_blocks</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
